--- a/开发相关/数采通道.xlsx
+++ b/开发相关/数采通道.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5EA66C-57CA-424D-BAC3-94ECE5215187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34183086-26C4-45FB-8ECE-9F34D34048F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="17550" windowHeight="11003" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="20250912" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1100,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6774FB1F-BE91-4CD0-9756-C6FDE37F72B0}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="7.9296875" bestFit="1" customWidth="1"/>
@@ -1404,20 +1413,30 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="M18">
+        <v>50</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="N19">
+        <f>M18/N18</f>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -1431,7 +1450,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -1445,7 +1464,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -1459,7 +1478,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1473,7 +1492,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1487,7 +1506,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -1498,7 +1517,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -1509,7 +1528,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>72</v>
       </c>

--- a/开发相关/数采通道.xlsx
+++ b/开发相关/数采通道.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34183086-26C4-45FB-8ECE-9F34D34048F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DAA9F2-4069-4FA9-B609-CC6556348826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="20250912" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="91">
   <si>
     <t>DEV1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -321,6 +322,14 @@
   </si>
   <si>
     <t>气缸2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1543,4 +1552,101 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D023DE44-2B4D-488E-8258-49F754E0A85E}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/开发相关/数采通道.xlsx
+++ b/开发相关/数采通道.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DAA9F2-4069-4FA9-B609-CC6556348826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F210496-780C-4B4F-9468-BB0B32000F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/开发相关/数采通道.xlsx
+++ b/开发相关/数采通道.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F210496-780C-4B4F-9468-BB0B32000F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9C974D-8B06-44E3-ACDE-50D29FB8629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="1230" windowWidth="19433" windowHeight="11602" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
